--- a/apps/web/public/examples/example-merging-digi.xlsx
+++ b/apps/web/public/examples/example-merging-digi.xlsx
@@ -457,7 +457,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:51:36</t>
+    <t>12:17:43</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-merging-digi.xlsx
+++ b/apps/web/public/examples/example-merging-digi.xlsx
@@ -457,7 +457,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>12:17:43</t>
+    <t>14:23:18</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-merging-digi.xlsx
+++ b/apps/web/public/examples/example-merging-digi.xlsx
@@ -457,7 +457,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>14:23:18</t>
+    <t>15:09:00</t>
   </si>
   <si>
     <t>Academic Year</t>
